--- a/backtest_runs/20260410_193731/by_symbol/MACTER/MACTER.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/MACTER/MACTER.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-1224.839999999987</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>101325.18</v>
@@ -633,7 +633,7 @@
         <v>-4594.88000000001</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>96730.3</v>
@@ -679,7 +679,7 @@
         <v>-6525.560000000005</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>90204.73999999999</v>
@@ -909,7 +909,7 @@
         <v>-788.8799999999906</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>101951.44</v>
@@ -955,7 +955,7 @@
         <v>-1913.38000000001</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>100038.06</v>
@@ -1047,7 +1047,7 @@
         <v>-1460.11999999999</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>99311.46000000002</v>
@@ -1185,7 +1185,7 @@
         <v>-1518.939999999995</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>100249.12</v>
@@ -1231,7 +1231,7 @@
         <v>-211.0600000000047</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>100038.06</v>
@@ -1277,7 +1277,7 @@
         <v>-5390.679999999995</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>94647.38</v>
@@ -1323,7 +1323,7 @@
         <v>-986.1000000000079</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>93661.28</v>
@@ -1415,7 +1415,7 @@
         <v>-3940.939999999995</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>93529.8</v>
@@ -1507,7 +1507,7 @@
         <v>-892.6799999999945</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>93560.94000000002</v>
@@ -1553,7 +1553,7 @@
         <v>-117.640000000011</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>93443.3</v>
@@ -1645,7 +1645,7 @@
         <v>-1456.659999999993</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>101159.1</v>
